--- a/売上目標設定シート_2026年6月.xlsx
+++ b/売上目標設定シート_2026年6月.xlsx
@@ -152,12 +152,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFC0"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFFFC0"/>
       </patternFill>
     </fill>
     <fill>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -261,13 +261,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,9 +286,7 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -316,7 +317,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3120,8 +3121,8 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3136,11 +3137,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>※ 黄色セルに数字を入力すると自動計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>※ 黄色セルを入力すると自動計算されます　　灰色セル＝自動算出（変更不要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>項目</t>
@@ -3149,21 +3150,27 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>更新見込み件数
-（変更可）</t>
+（自動算出）</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>回数券単価（円）
+          <t>実際の顧客数
+【手入力】</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>単価（円）
 【要入力】</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>小計（円）</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -3186,13 +3193,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="23">
-        <f>B5*C5</f>
+      <c r="E5" s="24">
+        <f>C5*D5</f>
         <v/>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>12枚綴り</t>
         </is>
@@ -3208,13 +3218,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="23">
-        <f>B6*C6</f>
+      <c r="E6" s="24">
+        <f>C6*D6</f>
         <v/>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>8枚綴り</t>
         </is>
@@ -3230,13 +3243,16 @@
         <v>15</v>
       </c>
       <c r="C7" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="23">
-        <f>B7*C7</f>
+      <c r="E7" s="24">
+        <f>C7*D7</f>
         <v/>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>4枚綴り</t>
         </is>
@@ -3252,29 +3268,32 @@
         <v>9</v>
       </c>
       <c r="C8" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="23">
-        <f>B8*C8</f>
+      <c r="E8" s="24">
+        <f>C8*D8</f>
         <v/>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>3枚綴り</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>既存顧客　小計</t>
         </is>
       </c>
-      <c r="D9" s="26">
-        <f>D5+D6+D7+D8</f>
+      <c r="E9" s="27">
+        <f>E5+E6+E7+E8</f>
         <v/>
       </c>
-      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="28" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -3284,61 +3303,62 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>新規顧客数</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" s="30" t="n"/>
       <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="23">
-        <f>B11*C11</f>
+      <c r="D11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="24">
+        <f>C11*D11</f>
         <v/>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>初回チケット平均単価</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>新規顧客　小計</t>
         </is>
       </c>
-      <c r="D12" s="31">
-        <f>D11</f>
+      <c r="E12" s="32">
+        <f>E11</f>
         <v/>
       </c>
-      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="28" t="n"/>
     </row>
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>▶ 当月　売上目標（最低見込み）</t>
         </is>
       </c>
-      <c r="D14" s="33">
-        <f>D9+D12</f>
+      <c r="E14" s="34">
+        <f>E9+E12</f>
         <v/>
       </c>
-      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="28" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>※ この数値は「確実に見込める最低限の売上」です。都度来院顧客・新規のアップセルなど上振れ分は含まれません。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>■ 当月更新見込み　件数サマリー（参考）</t>
         </is>
@@ -3377,174 +3397,175 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C19" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="41" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="38" t="n">
+      <c r="C20" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="E20" s="39" t="n">
+      <c r="E20" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="41" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="B21" s="37" t="n">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="38" t="n">
+      <c r="C21" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="39" t="n">
+      <c r="E21" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="41" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C22" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="41" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B23" s="44" t="n">
+      <c r="B23" s="45" t="n">
         <v>31</v>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="45" t="n">
         <v>22</v>
       </c>
-      <c r="E23" s="44" t="n">
+      <c r="E23" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="F23" s="44" t="n">
+      <c r="F23" s="45" t="n">
         <v>131</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>■ 入力手順</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="45" t="inlineStr">
-        <is>
-          <t>① 各回数券の「単価」（C5〜C8）を入力　→ 既存顧客の小計が自動計算されます</t>
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>① C列「実際の顧客数」（C5〜C8）を実績に合わせて入力（初期値はシステム算出値を自動セット）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="45" t="inlineStr">
-        <is>
-          <t>② 「新規顧客数」（B11）を実績または予測数に変更</t>
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>② D列「単価」（D5〜D8）を各回数券の金額に入力　→ E列「小計」が自動計算されます</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="45" t="inlineStr">
-        <is>
-          <t>③ 「初回チケット平均単価」（C11）を入力</t>
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>③ 新規顧客数（C11）と初回チケット平均単価（D11）を入力</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="45" t="inlineStr">
-        <is>
-          <t>④ B5〜B8 の「更新見込み件数」は変更可能（実態に合わせて上書きしてください）</t>
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>④ B列「更新見込み件数」はシステムが自動算出した参照値です（変更不要）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t>⑤ 売上目標セル（D14）に当月の最低見込み売上が表示されます</t>
+      <c r="A30" s="46" t="inlineStr">
+        <is>
+          <t>⑤ 売上目標セル（E14）に当月の最低見込み売上が表示されます</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4817,7 +4838,7 @@
       <c r="H37" s="18" t="inlineStr"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="42" t="n">
+      <c r="A38" s="43" t="n">
         <v>3078</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -4825,20 +4846,20 @@
           <t>オオジ　ミユキ</t>
         </is>
       </c>
-      <c r="C38" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="E38" s="42" t="n">
+      <c r="E38" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="42" t="inlineStr">
+      <c r="F38" s="43" t="inlineStr">
         <is>
           <t>2026/06/01</t>
         </is>
@@ -4851,7 +4872,7 @@
       <c r="H38" s="11" t="inlineStr"/>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="43" t="n">
+      <c r="A39" s="44" t="n">
         <v>3113</v>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -4859,20 +4880,20 @@
           <t>マツイ　サアヤ</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="E39" s="43" t="n">
+      <c r="E39" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="43" t="inlineStr">
+      <c r="F39" s="44" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
@@ -4885,7 +4906,7 @@
       <c r="H39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="42" t="n">
+      <c r="A40" s="43" t="n">
         <v>2337</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -4893,20 +4914,20 @@
           <t>フジイ　カヨコ</t>
         </is>
       </c>
-      <c r="C40" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D40" s="42" t="inlineStr">
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="E40" s="42" t="n">
+      <c r="E40" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="42" t="inlineStr">
+      <c r="F40" s="43" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
@@ -4919,7 +4940,7 @@
       <c r="H40" s="11" t="inlineStr"/>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="43" t="n">
+      <c r="A41" s="44" t="n">
         <v>3111</v>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -4927,20 +4948,20 @@
           <t>イトウ　ケンタ</t>
         </is>
       </c>
-      <c r="C41" s="43" t="inlineStr">
+      <c r="C41" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D41" s="43" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="E41" s="43" t="n">
+      <c r="E41" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="43" t="inlineStr">
+      <c r="F41" s="44" t="inlineStr">
         <is>
           <t>2026/06/03</t>
         </is>
@@ -4953,7 +4974,7 @@
       <c r="H41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="43" t="n">
+      <c r="A42" s="44" t="n">
         <v>3112</v>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -4961,20 +4982,20 @@
           <t>ノグチ　トシキ</t>
         </is>
       </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="C42" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="E42" s="43" t="n">
+      <c r="E42" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="43" t="inlineStr">
+      <c r="F42" s="44" t="inlineStr">
         <is>
           <t>2026/06/03</t>
         </is>
@@ -4987,7 +5008,7 @@
       <c r="H42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="42" t="n">
+      <c r="A43" s="43" t="n">
         <v>2453</v>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -4995,20 +5016,20 @@
           <t>ハセガワ　ミツアキ</t>
         </is>
       </c>
-      <c r="C43" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D43" s="42" t="inlineStr">
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>2026/05/05</t>
         </is>
       </c>
-      <c r="E43" s="42" t="n">
+      <c r="E43" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="42" t="inlineStr">
+      <c r="F43" s="43" t="inlineStr">
         <is>
           <t>2026/06/04</t>
         </is>
@@ -5021,7 +5042,7 @@
       <c r="H43" s="11" t="inlineStr"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="42" t="n">
+      <c r="A44" s="43" t="n">
         <v>3048</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -5029,20 +5050,20 @@
           <t>イノウエ　カズヒロ</t>
         </is>
       </c>
-      <c r="C44" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D44" s="42" t="inlineStr">
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>2026/04/25</t>
         </is>
       </c>
-      <c r="E44" s="42" t="n">
+      <c r="E44" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F44" s="42" t="inlineStr">
+      <c r="F44" s="43" t="inlineStr">
         <is>
           <t>2026/06/04</t>
         </is>
@@ -5055,7 +5076,7 @@
       <c r="H44" s="11" t="inlineStr"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="36" t="n">
+      <c r="A45" s="37" t="n">
         <v>2982</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -5063,20 +5084,20 @@
           <t>タカハシ　エミコ</t>
         </is>
       </c>
-      <c r="C45" s="36" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D45" s="36" t="inlineStr">
+      <c r="D45" s="37" t="inlineStr">
         <is>
           <t>2026/05/27</t>
         </is>
       </c>
-      <c r="E45" s="36" t="n">
+      <c r="E45" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="36" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>2026/06/06</t>
         </is>
@@ -5089,7 +5110,7 @@
       <c r="H45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="43" t="n">
+      <c r="A46" s="44" t="n">
         <v>3115</v>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -5097,20 +5118,20 @@
           <t>アラカワ　ダイスケ</t>
         </is>
       </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="C46" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="E46" s="43" t="n">
+      <c r="E46" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="F46" s="44" t="inlineStr">
         <is>
           <t>2026/06/07</t>
         </is>
@@ -5123,7 +5144,7 @@
       <c r="H46" s="14" t="inlineStr"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="42" t="n">
+      <c r="A47" s="43" t="n">
         <v>3099</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -5131,20 +5152,20 @@
           <t>ヨシノ　ショウコ</t>
         </is>
       </c>
-      <c r="C47" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D47" s="42" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="E47" s="42" t="n">
+      <c r="E47" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="42" t="inlineStr">
+      <c r="F47" s="43" t="inlineStr">
         <is>
           <t>2026/06/07</t>
         </is>
@@ -5157,7 +5178,7 @@
       <c r="H47" s="11" t="inlineStr"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="43" t="n">
+      <c r="A48" s="44" t="n">
         <v>3114</v>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -5165,20 +5186,20 @@
           <t>ツチヤ　ナツコ</t>
         </is>
       </c>
-      <c r="C48" s="43" t="inlineStr">
+      <c r="C48" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="D48" s="44" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="E48" s="43" t="n">
+      <c r="E48" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="F48" s="44" t="inlineStr">
         <is>
           <t>2026/06/08</t>
         </is>
@@ -5191,7 +5212,7 @@
       <c r="H48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="42" t="n">
+      <c r="A49" s="43" t="n">
         <v>2822</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -5199,20 +5220,20 @@
           <t>アオヤマ　ワカコ</t>
         </is>
       </c>
-      <c r="C49" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D49" s="42" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="E49" s="42" t="n">
+      <c r="E49" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="42" t="inlineStr">
+      <c r="F49" s="43" t="inlineStr">
         <is>
           <t>2026/06/09</t>
         </is>
@@ -5225,7 +5246,7 @@
       <c r="H49" s="11" t="inlineStr"/>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="42" t="n">
+      <c r="A50" s="43" t="n">
         <v>2394</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -5233,20 +5254,20 @@
           <t>コイズミ　ヒロノリ</t>
         </is>
       </c>
-      <c r="C50" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>2026/05/11</t>
         </is>
       </c>
-      <c r="E50" s="42" t="n">
+      <c r="E50" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="42" t="inlineStr">
+      <c r="F50" s="43" t="inlineStr">
         <is>
           <t>2026/06/10</t>
         </is>
@@ -5259,7 +5280,7 @@
       <c r="H50" s="11" t="inlineStr"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="42" t="n">
+      <c r="A51" s="43" t="n">
         <v>3025</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -5267,20 +5288,20 @@
           <t>ツルタ　カズコ</t>
         </is>
       </c>
-      <c r="C51" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D51" s="42" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="inlineStr">
         <is>
           <t>2026/05/03</t>
         </is>
       </c>
-      <c r="E51" s="42" t="n">
+      <c r="E51" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="42" t="inlineStr">
+      <c r="F51" s="43" t="inlineStr">
         <is>
           <t>2026/06/12</t>
         </is>
@@ -5293,7 +5314,7 @@
       <c r="H51" s="11" t="inlineStr"/>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="41" t="n">
+      <c r="A52" s="42" t="n">
         <v>2459</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -5301,20 +5322,20 @@
           <t>サイトウ　マサヒロ</t>
         </is>
       </c>
-      <c r="C52" s="41" t="inlineStr">
+      <c r="C52" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D52" s="41" t="inlineStr">
+      <c r="D52" s="42" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="E52" s="41" t="n">
+      <c r="E52" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="41" t="inlineStr">
+      <c r="F52" s="42" t="inlineStr">
         <is>
           <t>2026/06/13</t>
         </is>
@@ -5327,7 +5348,7 @@
       <c r="H52" s="8" t="inlineStr"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="42" t="n">
+      <c r="A53" s="43" t="n">
         <v>2974</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -5335,20 +5356,20 @@
           <t>セイノ　アキヒコ</t>
         </is>
       </c>
-      <c r="C53" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D53" s="42" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="E53" s="42" t="n">
+      <c r="E53" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F53" s="42" t="inlineStr">
+      <c r="F53" s="43" t="inlineStr">
         <is>
           <t>2026/06/14</t>
         </is>
@@ -5361,7 +5382,7 @@
       <c r="H53" s="11" t="inlineStr"/>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="41" t="n">
+      <c r="A54" s="42" t="n">
         <v>3057</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -5369,20 +5390,20 @@
           <t>コヤマ　ミキ</t>
         </is>
       </c>
-      <c r="C54" s="41" t="inlineStr">
+      <c r="C54" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D54" s="41" t="inlineStr">
+      <c r="D54" s="42" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="E54" s="41" t="n">
+      <c r="E54" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="41" t="inlineStr">
+      <c r="F54" s="42" t="inlineStr">
         <is>
           <t>2026/06/14</t>
         </is>
@@ -5395,7 +5416,7 @@
       <c r="H54" s="8" t="inlineStr"/>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="43" t="n">
+      <c r="A55" s="44" t="n">
         <v>3118</v>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -5403,20 +5424,20 @@
           <t>トキダ　ジュンイチ</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C55" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D55" s="44" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="E55" s="43" t="n">
+      <c r="E55" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F55" s="43" t="inlineStr">
+      <c r="F55" s="44" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
@@ -5429,7 +5450,7 @@
       <c r="H55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="43" t="n">
+      <c r="A56" s="44" t="n">
         <v>3120</v>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -5437,20 +5458,20 @@
           <t>ヨネヤマ　コウイチ</t>
         </is>
       </c>
-      <c r="C56" s="43" t="inlineStr">
+      <c r="C56" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="E56" s="43" t="n">
+      <c r="E56" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="43" t="inlineStr">
+      <c r="F56" s="44" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
@@ -5463,7 +5484,7 @@
       <c r="H56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="43" t="n">
+      <c r="A57" s="44" t="n">
         <v>3123</v>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -5471,20 +5492,20 @@
           <t>オオヒラ　タクミ</t>
         </is>
       </c>
-      <c r="C57" s="43" t="inlineStr">
+      <c r="C57" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
+      <c r="D57" s="44" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="E57" s="43" t="n">
+      <c r="E57" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F57" s="43" t="inlineStr">
+      <c r="F57" s="44" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
@@ -5497,7 +5518,7 @@
       <c r="H57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="42" t="n">
+      <c r="A58" s="43" t="n">
         <v>2961</v>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -5505,20 +5526,20 @@
           <t>ヨコハタ　カオリ</t>
         </is>
       </c>
-      <c r="C58" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D58" s="42" t="inlineStr">
+      <c r="C58" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>2026/05/06</t>
         </is>
       </c>
-      <c r="E58" s="42" t="n">
+      <c r="E58" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F58" s="42" t="inlineStr">
+      <c r="F58" s="43" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
@@ -5531,7 +5552,7 @@
       <c r="H58" s="11" t="inlineStr"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="43" t="n">
+      <c r="A59" s="44" t="n">
         <v>3117</v>
       </c>
       <c r="B59" s="14" t="inlineStr">
@@ -5539,20 +5560,20 @@
           <t>ヤマモト　サオリ</t>
         </is>
       </c>
-      <c r="C59" s="43" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>2026/05/27</t>
         </is>
       </c>
-      <c r="E59" s="43" t="n">
+      <c r="E59" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="43" t="inlineStr">
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>2026/06/16</t>
         </is>
@@ -5565,7 +5586,7 @@
       <c r="H59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="42" t="n">
+      <c r="A60" s="43" t="n">
         <v>2747</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -5573,20 +5594,20 @@
           <t>イノウエ　エミ</t>
         </is>
       </c>
-      <c r="C60" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D60" s="42" t="inlineStr">
+      <c r="C60" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="E60" s="42" t="n">
+      <c r="E60" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F60" s="42" t="inlineStr">
+      <c r="F60" s="43" t="inlineStr">
         <is>
           <t>2026/06/19</t>
         </is>
@@ -5599,7 +5620,7 @@
       <c r="H60" s="11" t="inlineStr"/>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="41" t="n">
+      <c r="A61" s="42" t="n">
         <v>2649</v>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -5607,20 +5628,20 @@
           <t>イワモト　タカヒト</t>
         </is>
       </c>
-      <c r="C61" s="41" t="inlineStr">
+      <c r="C61" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D61" s="41" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="E61" s="41" t="n">
+      <c r="E61" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="F61" s="41" t="inlineStr">
+      <c r="F61" s="42" t="inlineStr">
         <is>
           <t>2026/06/19</t>
         </is>
@@ -5633,7 +5654,7 @@
       <c r="H61" s="8" t="inlineStr"/>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="42" t="n">
+      <c r="A62" s="43" t="n">
         <v>3026</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -5641,20 +5662,20 @@
           <t>クラ　ユウジ</t>
         </is>
       </c>
-      <c r="C62" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D62" s="42" t="inlineStr">
+      <c r="C62" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="E62" s="42" t="n">
+      <c r="E62" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F62" s="42" t="inlineStr">
+      <c r="F62" s="43" t="inlineStr">
         <is>
           <t>2026/06/21</t>
         </is>
@@ -5667,7 +5688,7 @@
       <c r="H62" s="11" t="inlineStr"/>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="41" t="n">
+      <c r="A63" s="42" t="n">
         <v>2098</v>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -5675,20 +5696,20 @@
           <t>エビサワ　トモコ</t>
         </is>
       </c>
-      <c r="C63" s="41" t="inlineStr">
+      <c r="C63" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D63" s="41" t="inlineStr">
+      <c r="D63" s="42" t="inlineStr">
         <is>
           <t>2026/05/02</t>
         </is>
       </c>
-      <c r="E63" s="41" t="n">
+      <c r="E63" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="F63" s="41" t="inlineStr">
+      <c r="F63" s="42" t="inlineStr">
         <is>
           <t>2026/06/21</t>
         </is>
@@ -5701,7 +5722,7 @@
       <c r="H63" s="8" t="inlineStr"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="42" t="n">
+      <c r="A64" s="43" t="n">
         <v>3095</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -5709,20 +5730,20 @@
           <t>ババ　ナツホ</t>
         </is>
       </c>
-      <c r="C64" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D64" s="42" t="inlineStr">
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="E64" s="42" t="n">
+      <c r="E64" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F64" s="42" t="inlineStr">
+      <c r="F64" s="43" t="inlineStr">
         <is>
           <t>2026/06/22</t>
         </is>
@@ -5735,7 +5756,7 @@
       <c r="H64" s="11" t="inlineStr"/>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="42" t="n">
+      <c r="A65" s="43" t="n">
         <v>2830</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -5743,20 +5764,20 @@
           <t>シラホ　ケンイチ</t>
         </is>
       </c>
-      <c r="C65" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D65" s="42" t="inlineStr">
+      <c r="C65" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="E65" s="42" t="n">
+      <c r="E65" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F65" s="42" t="inlineStr">
+      <c r="F65" s="43" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
@@ -5769,7 +5790,7 @@
       <c r="H65" s="11" t="inlineStr"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="41" t="n">
+      <c r="A66" s="42" t="n">
         <v>2393</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -5777,20 +5798,20 @@
           <t>タケイ　ミツヒロ</t>
         </is>
       </c>
-      <c r="C66" s="41" t="inlineStr">
+      <c r="C66" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D66" s="41" t="inlineStr">
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="E66" s="41" t="n">
+      <c r="E66" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="41" t="inlineStr">
+      <c r="F66" s="42" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
@@ -5803,7 +5824,7 @@
       <c r="H66" s="8" t="inlineStr"/>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="42" t="n">
+      <c r="A67" s="43" t="n">
         <v>2007</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -5811,20 +5832,20 @@
           <t>ツチダ　トモミ</t>
         </is>
       </c>
-      <c r="C67" s="42" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D67" s="42" t="inlineStr">
+      <c r="C67" s="43" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="E67" s="42" t="n">
+      <c r="E67" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="F67" s="42" t="inlineStr">
+      <c r="F67" s="43" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
@@ -5837,7 +5858,7 @@
       <c r="H67" s="11" t="inlineStr"/>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="41" t="n">
+      <c r="A68" s="42" t="n">
         <v>2864</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -5845,20 +5866,20 @@
           <t>オヌキ　コウジ</t>
         </is>
       </c>
-      <c r="C68" s="41" t="inlineStr">
+      <c r="C68" s="42" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D68" s="41" t="inlineStr">
+      <c r="D68" s="42" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="E68" s="41" t="n">
+      <c r="E68" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="F68" s="41" t="inlineStr">
+      <c r="F68" s="42" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
@@ -5871,2382 +5892,2382 @@
       <c r="H68" s="8" t="inlineStr"/>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="39" t="n">
+      <c r="A69" s="40" t="n">
         <v>2348</v>
       </c>
-      <c r="B69" s="24" t="inlineStr">
+      <c r="B69" s="25" t="inlineStr">
         <is>
           <t>コダマ　ショウ</t>
         </is>
       </c>
-      <c r="C69" s="39" t="inlineStr">
+      <c r="C69" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D69" s="39" t="inlineStr">
+      <c r="D69" s="40" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="E69" s="39" t="n">
+      <c r="E69" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F69" s="39" t="inlineStr">
+      <c r="F69" s="40" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="G69" s="24" t="inlineStr">
+      <c r="G69" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H69" s="24" t="inlineStr"/>
+      <c r="H69" s="25" t="inlineStr"/>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="39" t="n">
+      <c r="A70" s="40" t="n">
         <v>2937</v>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B70" s="25" t="inlineStr">
         <is>
           <t>カワゾエ　イチロウ</t>
         </is>
       </c>
-      <c r="C70" s="39" t="inlineStr">
+      <c r="C70" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D70" s="39" t="inlineStr">
+      <c r="D70" s="40" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="E70" s="39" t="n">
+      <c r="E70" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F70" s="39" t="inlineStr">
+      <c r="F70" s="40" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="G70" s="24" t="inlineStr">
+      <c r="G70" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H70" s="24" t="inlineStr"/>
+      <c r="H70" s="25" t="inlineStr"/>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="39" t="n">
+      <c r="A71" s="40" t="n">
         <v>2537</v>
       </c>
-      <c r="B71" s="24" t="inlineStr">
+      <c r="B71" s="25" t="inlineStr">
         <is>
           <t>タニグチ　アキカズ</t>
         </is>
       </c>
-      <c r="C71" s="39" t="inlineStr">
+      <c r="C71" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D71" s="39" t="inlineStr">
+      <c r="D71" s="40" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="E71" s="39" t="n">
+      <c r="E71" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="39" t="inlineStr">
+      <c r="F71" s="40" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="G71" s="24" t="inlineStr">
+      <c r="G71" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H71" s="24" t="inlineStr"/>
+      <c r="H71" s="25" t="inlineStr"/>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="39" t="n">
+      <c r="A72" s="40" t="n">
         <v>3098</v>
       </c>
-      <c r="B72" s="24" t="inlineStr">
+      <c r="B72" s="25" t="inlineStr">
         <is>
           <t>ヤマモト　ヨシノリ</t>
         </is>
       </c>
-      <c r="C72" s="39" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D72" s="39" t="inlineStr">
+      <c r="D72" s="40" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="E72" s="39" t="n">
+      <c r="E72" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="39" t="inlineStr">
+      <c r="F72" s="40" t="inlineStr">
         <is>
           <t>2026/07/05</t>
         </is>
       </c>
-      <c r="G72" s="24" t="inlineStr">
+      <c r="G72" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H72" s="24" t="inlineStr"/>
+      <c r="H72" s="25" t="inlineStr"/>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="39" t="n">
+      <c r="A73" s="40" t="n">
         <v>2761</v>
       </c>
-      <c r="B73" s="24" t="inlineStr">
+      <c r="B73" s="25" t="inlineStr">
         <is>
           <t>ノダ　カズエ</t>
         </is>
       </c>
-      <c r="C73" s="39" t="inlineStr">
+      <c r="C73" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D73" s="39" t="inlineStr">
+      <c r="D73" s="40" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="E73" s="39" t="n">
+      <c r="E73" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F73" s="39" t="inlineStr">
+      <c r="F73" s="40" t="inlineStr">
         <is>
           <t>2026/07/09</t>
         </is>
       </c>
-      <c r="G73" s="24" t="inlineStr">
+      <c r="G73" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H73" s="24" t="inlineStr"/>
+      <c r="H73" s="25" t="inlineStr"/>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="39" t="n">
+      <c r="A74" s="40" t="n">
         <v>2301</v>
       </c>
-      <c r="B74" s="24" t="inlineStr">
+      <c r="B74" s="25" t="inlineStr">
         <is>
           <t>キヨカワ　タエ</t>
         </is>
       </c>
-      <c r="C74" s="39" t="inlineStr">
+      <c r="C74" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D74" s="39" t="inlineStr">
+      <c r="D74" s="40" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="E74" s="39" t="n">
+      <c r="E74" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F74" s="39" t="inlineStr">
+      <c r="F74" s="40" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
-      <c r="G74" s="24" t="inlineStr">
+      <c r="G74" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H74" s="24" t="inlineStr"/>
+      <c r="H74" s="25" t="inlineStr"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="39" t="n">
+      <c r="A75" s="40" t="n">
         <v>2377</v>
       </c>
-      <c r="B75" s="24" t="inlineStr">
+      <c r="B75" s="25" t="inlineStr">
         <is>
           <t>イシモリ　キヨタカ</t>
         </is>
       </c>
-      <c r="C75" s="39" t="inlineStr">
+      <c r="C75" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D75" s="39" t="inlineStr">
+      <c r="D75" s="40" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="E75" s="39" t="n">
+      <c r="E75" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F75" s="39" t="inlineStr">
+      <c r="F75" s="40" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
-      <c r="G75" s="24" t="inlineStr">
+      <c r="G75" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H75" s="24" t="inlineStr"/>
+      <c r="H75" s="25" t="inlineStr"/>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="39" t="n">
+      <c r="A76" s="40" t="n">
         <v>3091</v>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B76" s="25" t="inlineStr">
         <is>
           <t>クラタ　ミノリ</t>
         </is>
       </c>
-      <c r="C76" s="39" t="inlineStr">
+      <c r="C76" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D76" s="39" t="inlineStr">
+      <c r="D76" s="40" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="E76" s="39" t="n">
+      <c r="E76" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F76" s="39" t="inlineStr">
+      <c r="F76" s="40" t="inlineStr">
         <is>
           <t>2026/07/16</t>
         </is>
       </c>
-      <c r="G76" s="24" t="inlineStr">
+      <c r="G76" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H76" s="24" t="inlineStr"/>
+      <c r="H76" s="25" t="inlineStr"/>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="39" t="n">
+      <c r="A77" s="40" t="n">
         <v>3096</v>
       </c>
-      <c r="B77" s="24" t="inlineStr">
+      <c r="B77" s="25" t="inlineStr">
         <is>
           <t>イワサキ　ミサコ</t>
         </is>
       </c>
-      <c r="C77" s="39" t="inlineStr">
+      <c r="C77" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D77" s="39" t="inlineStr">
+      <c r="D77" s="40" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="E77" s="39" t="n">
+      <c r="E77" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F77" s="39" t="inlineStr">
+      <c r="F77" s="40" t="inlineStr">
         <is>
           <t>2026/07/18</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
+      <c r="G77" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H77" s="24" t="inlineStr"/>
+      <c r="H77" s="25" t="inlineStr"/>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="39" t="n">
+      <c r="A78" s="40" t="n">
         <v>3061</v>
       </c>
-      <c r="B78" s="24" t="inlineStr">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>マスダ　ハツミ</t>
         </is>
       </c>
-      <c r="C78" s="39" t="inlineStr">
+      <c r="C78" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D78" s="39" t="inlineStr">
+      <c r="D78" s="40" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="E78" s="39" t="n">
+      <c r="E78" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F78" s="39" t="inlineStr">
+      <c r="F78" s="40" t="inlineStr">
         <is>
           <t>2026/07/21</t>
         </is>
       </c>
-      <c r="G78" s="24" t="inlineStr">
+      <c r="G78" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H78" s="24" t="inlineStr"/>
+      <c r="H78" s="25" t="inlineStr"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="39" t="n">
+      <c r="A79" s="40" t="n">
         <v>2308</v>
       </c>
-      <c r="B79" s="24" t="inlineStr">
+      <c r="B79" s="25" t="inlineStr">
         <is>
           <t>オオヤマ　シズオ</t>
         </is>
       </c>
-      <c r="C79" s="39" t="inlineStr">
+      <c r="C79" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D79" s="39" t="inlineStr">
+      <c r="D79" s="40" t="inlineStr">
         <is>
           <t>2026/05/02</t>
         </is>
       </c>
-      <c r="E79" s="39" t="n">
+      <c r="E79" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="F79" s="39" t="inlineStr">
+      <c r="F79" s="40" t="inlineStr">
         <is>
           <t>2026/07/21</t>
         </is>
       </c>
-      <c r="G79" s="24" t="inlineStr">
+      <c r="G79" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H79" s="24" t="inlineStr"/>
+      <c r="H79" s="25" t="inlineStr"/>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="39" t="n">
+      <c r="A80" s="40" t="n">
         <v>2520</v>
       </c>
-      <c r="B80" s="24" t="inlineStr">
+      <c r="B80" s="25" t="inlineStr">
         <is>
           <t>ニッタ　ユウヤ</t>
         </is>
       </c>
-      <c r="C80" s="39" t="inlineStr">
+      <c r="C80" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D80" s="39" t="inlineStr">
+      <c r="D80" s="40" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="E80" s="39" t="n">
+      <c r="E80" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F80" s="39" t="inlineStr">
+      <c r="F80" s="40" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="G80" s="24" t="inlineStr">
+      <c r="G80" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H80" s="24" t="inlineStr"/>
+      <c r="H80" s="25" t="inlineStr"/>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="39" t="n">
+      <c r="A81" s="40" t="n">
         <v>2875</v>
       </c>
-      <c r="B81" s="24" t="inlineStr">
+      <c r="B81" s="25" t="inlineStr">
         <is>
           <t>ムカイ　ヒロト</t>
         </is>
       </c>
-      <c r="C81" s="39" t="inlineStr">
+      <c r="C81" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D81" s="39" t="inlineStr">
+      <c r="D81" s="40" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="E81" s="39" t="n">
+      <c r="E81" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="F81" s="39" t="inlineStr">
+      <c r="F81" s="40" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="G81" s="24" t="inlineStr">
+      <c r="G81" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H81" s="24" t="inlineStr"/>
+      <c r="H81" s="25" t="inlineStr"/>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="39" t="n">
+      <c r="A82" s="40" t="n">
         <v>5294</v>
       </c>
-      <c r="B82" s="24" t="inlineStr">
+      <c r="B82" s="25" t="inlineStr">
         <is>
           <t>クマガイ　ケン</t>
         </is>
       </c>
-      <c r="C82" s="39" t="inlineStr">
+      <c r="C82" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D82" s="39" t="inlineStr">
+      <c r="D82" s="40" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="E82" s="39" t="n">
+      <c r="E82" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="F82" s="39" t="inlineStr">
+      <c r="F82" s="40" t="inlineStr">
         <is>
           <t>2026/07/24</t>
         </is>
       </c>
-      <c r="G82" s="24" t="inlineStr">
+      <c r="G82" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H82" s="24" t="inlineStr"/>
+      <c r="H82" s="25" t="inlineStr"/>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="39" t="n">
+      <c r="A83" s="40" t="n">
         <v>2450</v>
       </c>
-      <c r="B83" s="24" t="inlineStr">
+      <c r="B83" s="25" t="inlineStr">
         <is>
           <t>アリフク　ジュン</t>
         </is>
       </c>
-      <c r="C83" s="39" t="inlineStr">
+      <c r="C83" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D83" s="39" t="inlineStr">
+      <c r="D83" s="40" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="E83" s="39" t="n">
+      <c r="E83" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="F83" s="39" t="inlineStr">
+      <c r="F83" s="40" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="G83" s="24" t="inlineStr">
+      <c r="G83" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H83" s="24" t="inlineStr"/>
+      <c r="H83" s="25" t="inlineStr"/>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="39" t="n">
+      <c r="A84" s="40" t="n">
         <v>3104</v>
       </c>
-      <c r="B84" s="24" t="inlineStr">
+      <c r="B84" s="25" t="inlineStr">
         <is>
           <t>タナカ　チサト</t>
         </is>
       </c>
-      <c r="C84" s="39" t="inlineStr">
+      <c r="C84" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D84" s="39" t="inlineStr">
+      <c r="D84" s="40" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="E84" s="39" t="n">
+      <c r="E84" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="F84" s="39" t="inlineStr">
+      <c r="F84" s="40" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="G84" s="24" t="inlineStr">
+      <c r="G84" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H84" s="24" t="inlineStr"/>
+      <c r="H84" s="25" t="inlineStr"/>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="39" t="n">
+      <c r="A85" s="40" t="n">
         <v>3103</v>
       </c>
-      <c r="B85" s="24" t="inlineStr">
+      <c r="B85" s="25" t="inlineStr">
         <is>
           <t>トミナガ　タイチ</t>
         </is>
       </c>
-      <c r="C85" s="39" t="inlineStr">
+      <c r="C85" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D85" s="39" t="inlineStr">
+      <c r="D85" s="40" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="E85" s="39" t="n">
+      <c r="E85" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="F85" s="39" t="inlineStr">
+      <c r="F85" s="40" t="inlineStr">
         <is>
           <t>2026/08/01</t>
         </is>
       </c>
-      <c r="G85" s="24" t="inlineStr">
+      <c r="G85" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H85" s="24" t="inlineStr"/>
+      <c r="H85" s="25" t="inlineStr"/>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="39" t="n">
+      <c r="A86" s="40" t="n">
         <v>3102</v>
       </c>
-      <c r="B86" s="24" t="inlineStr">
+      <c r="B86" s="25" t="inlineStr">
         <is>
           <t>タカツカ　ミホ</t>
         </is>
       </c>
-      <c r="C86" s="39" t="inlineStr">
+      <c r="C86" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D86" s="39" t="inlineStr">
+      <c r="D86" s="40" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="E86" s="39" t="n">
+      <c r="E86" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="F86" s="39" t="inlineStr">
+      <c r="F86" s="40" t="inlineStr">
         <is>
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="G86" s="24" t="inlineStr">
+      <c r="G86" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H86" s="24" t="inlineStr"/>
+      <c r="H86" s="25" t="inlineStr"/>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="39" t="n">
+      <c r="A87" s="40" t="n">
         <v>2148</v>
       </c>
-      <c r="B87" s="24" t="inlineStr">
+      <c r="B87" s="25" t="inlineStr">
         <is>
           <t>スヤマ　ヨシユキ</t>
         </is>
       </c>
-      <c r="C87" s="39" t="inlineStr">
+      <c r="C87" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D87" s="39" t="inlineStr">
+      <c r="D87" s="40" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="E87" s="39" t="n">
+      <c r="E87" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="F87" s="39" t="inlineStr">
+      <c r="F87" s="40" t="inlineStr">
         <is>
           <t>2026/08/04</t>
         </is>
       </c>
-      <c r="G87" s="24" t="inlineStr">
+      <c r="G87" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H87" s="24" t="inlineStr"/>
+      <c r="H87" s="25" t="inlineStr"/>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="39" t="n">
+      <c r="A88" s="40" t="n">
         <v>3089</v>
       </c>
-      <c r="B88" s="24" t="inlineStr">
+      <c r="B88" s="25" t="inlineStr">
         <is>
           <t>デガワ　ハルト</t>
         </is>
       </c>
-      <c r="C88" s="39" t="inlineStr">
+      <c r="C88" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D88" s="39" t="inlineStr">
+      <c r="D88" s="40" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="E88" s="39" t="n">
+      <c r="E88" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="F88" s="39" t="inlineStr">
+      <c r="F88" s="40" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="G88" s="24" t="inlineStr">
+      <c r="G88" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H88" s="24" t="inlineStr"/>
+      <c r="H88" s="25" t="inlineStr"/>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="39" t="n">
+      <c r="A89" s="40" t="n">
         <v>2917</v>
       </c>
-      <c r="B89" s="24" t="inlineStr">
+      <c r="B89" s="25" t="inlineStr">
         <is>
           <t>クス　フミエ</t>
         </is>
       </c>
-      <c r="C89" s="39" t="inlineStr">
+      <c r="C89" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D89" s="39" t="inlineStr">
+      <c r="D89" s="40" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="E89" s="39" t="n">
+      <c r="E89" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="F89" s="39" t="inlineStr">
+      <c r="F89" s="40" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="G89" s="24" t="inlineStr">
+      <c r="G89" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H89" s="24" t="inlineStr"/>
+      <c r="H89" s="25" t="inlineStr"/>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="39" t="n">
+      <c r="A90" s="40" t="n">
         <v>3006</v>
       </c>
-      <c r="B90" s="24" t="inlineStr">
+      <c r="B90" s="25" t="inlineStr">
         <is>
           <t>ワダ　シュウセイ</t>
         </is>
       </c>
-      <c r="C90" s="39" t="inlineStr">
+      <c r="C90" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D90" s="39" t="inlineStr">
+      <c r="D90" s="40" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="E90" s="39" t="n">
+      <c r="E90" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="F90" s="39" t="inlineStr">
+      <c r="F90" s="40" t="inlineStr">
         <is>
           <t>2026/09/19</t>
         </is>
       </c>
-      <c r="G90" s="24" t="inlineStr">
+      <c r="G90" s="25" t="inlineStr">
         <is>
           <t>翌月以降</t>
         </is>
       </c>
-      <c r="H90" s="24" t="inlineStr"/>
+      <c r="H90" s="25" t="inlineStr"/>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="39" t="n">
+      <c r="A91" s="40" t="n">
         <v>2014</v>
       </c>
-      <c r="B91" s="24" t="inlineStr">
+      <c r="B91" s="25" t="inlineStr">
         <is>
           <t>サイトウ　ヨシエ</t>
         </is>
       </c>
-      <c r="C91" s="39" t="inlineStr">
+      <c r="C91" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D91" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E91" s="39" t="n">
+      <c r="D91" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="F91" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="24" t="inlineStr">
+      <c r="F91" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H91" s="24" t="inlineStr">
+      <c r="H91" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="39" t="n">
+      <c r="A92" s="40" t="n">
         <v>2035</v>
       </c>
-      <c r="B92" s="24" t="inlineStr">
+      <c r="B92" s="25" t="inlineStr">
         <is>
           <t>ハギワラ　マユミ</t>
         </is>
       </c>
-      <c r="C92" s="39" t="inlineStr">
+      <c r="C92" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D92" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="39" t="n">
+      <c r="D92" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F92" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
+      <c r="F92" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H92" s="24" t="inlineStr">
+      <c r="H92" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="39" t="n">
+      <c r="A93" s="40" t="n">
         <v>2039</v>
       </c>
-      <c r="B93" s="24" t="inlineStr">
+      <c r="B93" s="25" t="inlineStr">
         <is>
           <t>タカナシ　エイイチ</t>
         </is>
       </c>
-      <c r="C93" s="39" t="inlineStr">
+      <c r="C93" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D93" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E93" s="39" t="n">
+      <c r="D93" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F93" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="24" t="inlineStr">
+      <c r="F93" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H93" s="24" t="inlineStr">
+      <c r="H93" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="39" t="n">
+      <c r="A94" s="40" t="n">
         <v>2043</v>
       </c>
-      <c r="B94" s="24" t="inlineStr">
+      <c r="B94" s="25" t="inlineStr">
         <is>
           <t>ナカタ　ヨウコ</t>
         </is>
       </c>
-      <c r="C94" s="39" t="inlineStr">
+      <c r="C94" s="40" t="inlineStr">
         <is>
           <t>12回券</t>
         </is>
       </c>
-      <c r="D94" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E94" s="39" t="n">
+      <c r="D94" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F94" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="24" t="inlineStr">
+      <c r="F94" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H94" s="24" t="inlineStr">
+      <c r="H94" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="39" t="n">
+      <c r="A95" s="40" t="n">
         <v>2023</v>
       </c>
-      <c r="B95" s="24" t="inlineStr">
+      <c r="B95" s="25" t="inlineStr">
         <is>
           <t>ヒガ　ケイスケ</t>
         </is>
       </c>
-      <c r="C95" s="39" t="inlineStr">
+      <c r="C95" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D95" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E95" s="39" t="n">
+      <c r="D95" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="24" t="inlineStr">
+      <c r="F95" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H95" s="24" t="inlineStr">
+      <c r="H95" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="39" t="n">
+      <c r="A96" s="40" t="n">
         <v>2024</v>
       </c>
-      <c r="B96" s="24" t="inlineStr">
+      <c r="B96" s="25" t="inlineStr">
         <is>
           <t>ヤマゾエ　タツロウ</t>
         </is>
       </c>
-      <c r="C96" s="39" t="inlineStr">
+      <c r="C96" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D96" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E96" s="39" t="n">
+      <c r="D96" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E96" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F96" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G96" s="24" t="inlineStr">
+      <c r="F96" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H96" s="24" t="inlineStr">
+      <c r="H96" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="39" t="n">
+      <c r="A97" s="40" t="n">
         <v>2028</v>
       </c>
-      <c r="B97" s="24" t="inlineStr">
+      <c r="B97" s="25" t="inlineStr">
         <is>
           <t>ニシ　トモヒロ</t>
         </is>
       </c>
-      <c r="C97" s="39" t="inlineStr">
+      <c r="C97" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D97" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E97" s="39" t="n">
+      <c r="D97" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F97" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" s="24" t="inlineStr">
+      <c r="F97" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H97" s="24" t="inlineStr">
+      <c r="H97" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="39" t="n">
+      <c r="A98" s="40" t="n">
         <v>2029</v>
       </c>
-      <c r="B98" s="24" t="inlineStr">
+      <c r="B98" s="25" t="inlineStr">
         <is>
           <t>カネコ　ユミ</t>
         </is>
       </c>
-      <c r="C98" s="39" t="inlineStr">
+      <c r="C98" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E98" s="39" t="n">
+      <c r="D98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="24" t="inlineStr">
+      <c r="F98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H98" s="24" t="inlineStr">
+      <c r="H98" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="39" t="n">
+      <c r="A99" s="40" t="n">
         <v>2031</v>
       </c>
-      <c r="B99" s="24" t="inlineStr">
+      <c r="B99" s="25" t="inlineStr">
         <is>
           <t>ヒラマツ　シュウイチ</t>
         </is>
       </c>
-      <c r="C99" s="39" t="inlineStr">
+      <c r="C99" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D99" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E99" s="39" t="n">
+      <c r="D99" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="24" t="inlineStr">
+      <c r="F99" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H99" s="24" t="inlineStr">
+      <c r="H99" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="39" t="n">
+      <c r="A100" s="40" t="n">
         <v>2032</v>
       </c>
-      <c r="B100" s="24" t="inlineStr">
+      <c r="B100" s="25" t="inlineStr">
         <is>
           <t>センダ　マコト</t>
         </is>
       </c>
-      <c r="C100" s="39" t="inlineStr">
+      <c r="C100" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D100" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E100" s="39" t="n">
+      <c r="D100" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E100" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G100" s="24" t="inlineStr">
+      <c r="F100" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H100" s="24" t="inlineStr">
+      <c r="H100" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="39" t="n">
+      <c r="A101" s="40" t="n">
         <v>2038</v>
       </c>
-      <c r="B101" s="24" t="inlineStr">
+      <c r="B101" s="25" t="inlineStr">
         <is>
           <t>フナバシ　ミチコ</t>
         </is>
       </c>
-      <c r="C101" s="39" t="inlineStr">
+      <c r="C101" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D101" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E101" s="39" t="n">
+      <c r="D101" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G101" s="24" t="inlineStr">
+      <c r="F101" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H101" s="24" t="inlineStr">
+      <c r="H101" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="39" t="n">
+      <c r="A102" s="40" t="n">
         <v>2047</v>
       </c>
-      <c r="B102" s="24" t="inlineStr">
+      <c r="B102" s="25" t="inlineStr">
         <is>
           <t>ヒラバヤシ　ヨシミ</t>
         </is>
       </c>
-      <c r="C102" s="39" t="inlineStr">
+      <c r="C102" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D102" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E102" s="39" t="n">
+      <c r="D102" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G102" s="24" t="inlineStr">
+      <c r="F102" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H102" s="24" t="inlineStr">
+      <c r="H102" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="39" t="n">
+      <c r="A103" s="40" t="n">
         <v>2050</v>
       </c>
-      <c r="B103" s="24" t="inlineStr">
+      <c r="B103" s="25" t="inlineStr">
         <is>
           <t>タカナシ　チエコ</t>
         </is>
       </c>
-      <c r="C103" s="39" t="inlineStr">
+      <c r="C103" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D103" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E103" s="39" t="n">
+      <c r="D103" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F103" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G103" s="24" t="inlineStr">
+      <c r="F103" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H103" s="24" t="inlineStr">
+      <c r="H103" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="39" t="n">
+      <c r="A104" s="40" t="n">
         <v>2052</v>
       </c>
-      <c r="B104" s="24" t="inlineStr">
+      <c r="B104" s="25" t="inlineStr">
         <is>
           <t>ナカムラ　トシアキ</t>
         </is>
       </c>
-      <c r="C104" s="39" t="inlineStr">
+      <c r="C104" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D104" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E104" s="39" t="n">
+      <c r="D104" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="24" t="inlineStr">
+      <c r="F104" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H104" s="24" t="inlineStr">
+      <c r="H104" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="39" t="n">
+      <c r="A105" s="40" t="n">
         <v>2055</v>
       </c>
-      <c r="B105" s="24" t="inlineStr">
+      <c r="B105" s="25" t="inlineStr">
         <is>
           <t>カミヤマ　サトル</t>
         </is>
       </c>
-      <c r="C105" s="39" t="inlineStr">
+      <c r="C105" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D105" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E105" s="39" t="n">
+      <c r="D105" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G105" s="24" t="inlineStr">
+      <c r="F105" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H105" s="24" t="inlineStr">
+      <c r="H105" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="39" t="n">
+      <c r="A106" s="40" t="n">
         <v>2056</v>
       </c>
-      <c r="B106" s="24" t="inlineStr">
+      <c r="B106" s="25" t="inlineStr">
         <is>
           <t>ソエカワ　ゴロウ</t>
         </is>
       </c>
-      <c r="C106" s="39" t="inlineStr">
+      <c r="C106" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D106" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E106" s="39" t="n">
+      <c r="D106" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F106" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G106" s="24" t="inlineStr">
+      <c r="F106" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H106" s="24" t="inlineStr">
+      <c r="H106" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="39" t="n">
+      <c r="A107" s="40" t="n">
         <v>2059</v>
       </c>
-      <c r="B107" s="24" t="inlineStr">
+      <c r="B107" s="25" t="inlineStr">
         <is>
           <t>ノガワ　マユミ</t>
         </is>
       </c>
-      <c r="C107" s="39" t="inlineStr">
+      <c r="C107" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D107" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E107" s="39" t="n">
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F107" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G107" s="24" t="inlineStr">
+      <c r="F107" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H107" s="24" t="inlineStr">
+      <c r="H107" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="39" t="n">
+      <c r="A108" s="40" t="n">
         <v>2060</v>
       </c>
-      <c r="B108" s="24" t="inlineStr">
+      <c r="B108" s="25" t="inlineStr">
         <is>
           <t>サトウ　リキ</t>
         </is>
       </c>
-      <c r="C108" s="39" t="inlineStr">
+      <c r="C108" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D108" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E108" s="39" t="n">
+      <c r="D108" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G108" s="24" t="inlineStr">
+      <c r="F108" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H108" s="24" t="inlineStr">
+      <c r="H108" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="39" t="n">
+      <c r="A109" s="40" t="n">
         <v>2061</v>
       </c>
-      <c r="B109" s="24" t="inlineStr">
+      <c r="B109" s="25" t="inlineStr">
         <is>
           <t>サトウ　ケイ</t>
         </is>
       </c>
-      <c r="C109" s="39" t="inlineStr">
+      <c r="C109" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D109" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E109" s="39" t="n">
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G109" s="24" t="inlineStr">
+      <c r="F109" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H109" s="24" t="inlineStr">
+      <c r="H109" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="39" t="n">
+      <c r="A110" s="40" t="n">
         <v>2064</v>
       </c>
-      <c r="B110" s="24" t="inlineStr">
+      <c r="B110" s="25" t="inlineStr">
         <is>
           <t>ヤマグチ　ソノコ</t>
         </is>
       </c>
-      <c r="C110" s="39" t="inlineStr">
+      <c r="C110" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D110" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E110" s="39" t="n">
+      <c r="D110" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G110" s="24" t="inlineStr">
+      <c r="F110" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H110" s="24" t="inlineStr">
+      <c r="H110" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="39" t="n">
+      <c r="A111" s="40" t="n">
         <v>2071</v>
       </c>
-      <c r="B111" s="24" t="inlineStr">
+      <c r="B111" s="25" t="inlineStr">
         <is>
           <t>ゴトウ　ナツミ</t>
         </is>
       </c>
-      <c r="C111" s="39" t="inlineStr">
+      <c r="C111" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D111" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E111" s="39" t="n">
+      <c r="D111" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G111" s="24" t="inlineStr">
+      <c r="F111" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H111" s="24" t="inlineStr">
+      <c r="H111" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="39" t="n">
+      <c r="A112" s="40" t="n">
         <v>2073</v>
       </c>
-      <c r="B112" s="24" t="inlineStr">
+      <c r="B112" s="25" t="inlineStr">
         <is>
           <t>サカモト　カツミ</t>
         </is>
       </c>
-      <c r="C112" s="39" t="inlineStr">
+      <c r="C112" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D112" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E112" s="39" t="n">
+      <c r="D112" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F112" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G112" s="24" t="inlineStr">
+      <c r="F112" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G112" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H112" s="24" t="inlineStr">
+      <c r="H112" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="39" t="n">
+      <c r="A113" s="40" t="n">
         <v>2074</v>
       </c>
-      <c r="B113" s="24" t="inlineStr">
+      <c r="B113" s="25" t="inlineStr">
         <is>
           <t>サイ　トモヤ</t>
         </is>
       </c>
-      <c r="C113" s="39" t="inlineStr">
+      <c r="C113" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D113" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E113" s="39" t="n">
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="F113" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G113" s="24" t="inlineStr">
+      <c r="F113" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H113" s="24" t="inlineStr">
+      <c r="H113" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="39" t="n">
+      <c r="A114" s="40" t="n">
         <v>2075</v>
       </c>
-      <c r="B114" s="24" t="inlineStr">
+      <c r="B114" s="25" t="inlineStr">
         <is>
           <t>オハラ　トモヒロ</t>
         </is>
       </c>
-      <c r="C114" s="39" t="inlineStr">
+      <c r="C114" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D114" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E114" s="39" t="n">
+      <c r="D114" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G114" s="24" t="inlineStr">
+      <c r="F114" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H114" s="24" t="inlineStr">
+      <c r="H114" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="39" t="n">
+      <c r="A115" s="40" t="n">
         <v>2889</v>
       </c>
-      <c r="B115" s="24" t="inlineStr">
+      <c r="B115" s="25" t="inlineStr">
         <is>
           <t>モトハシ　ケンイチ</t>
         </is>
       </c>
-      <c r="C115" s="39" t="inlineStr">
+      <c r="C115" s="40" t="inlineStr">
         <is>
           <t>3回券</t>
         </is>
       </c>
-      <c r="D115" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E115" s="39" t="n">
+      <c r="D115" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G115" s="24" t="inlineStr">
+      <c r="F115" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H115" s="24" t="inlineStr">
+      <c r="H115" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="39" t="n">
+      <c r="A116" s="40" t="n">
         <v>2021</v>
       </c>
-      <c r="B116" s="24" t="inlineStr">
+      <c r="B116" s="25" t="inlineStr">
         <is>
           <t>オオガヤ　シュンジ</t>
         </is>
       </c>
-      <c r="C116" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D116" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E116" s="39" t="n">
+      <c r="C116" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D116" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G116" s="24" t="inlineStr">
+      <c r="F116" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H116" s="24" t="inlineStr">
+      <c r="H116" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="39" t="n">
+      <c r="A117" s="40" t="n">
         <v>2026</v>
       </c>
-      <c r="B117" s="24" t="inlineStr">
+      <c r="B117" s="25" t="inlineStr">
         <is>
           <t>ミズキ　ヨシコ</t>
         </is>
       </c>
-      <c r="C117" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D117" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E117" s="39" t="n">
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F117" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G117" s="24" t="inlineStr">
+      <c r="F117" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H117" s="24" t="inlineStr">
+      <c r="H117" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="39" t="n">
+      <c r="A118" s="40" t="n">
         <v>2027</v>
       </c>
-      <c r="B118" s="24" t="inlineStr">
+      <c r="B118" s="25" t="inlineStr">
         <is>
           <t>ヤナモト　カズキ</t>
         </is>
       </c>
-      <c r="C118" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D118" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E118" s="39" t="n">
+      <c r="C118" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D118" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F118" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G118" s="24" t="inlineStr">
+      <c r="F118" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H118" s="24" t="inlineStr">
+      <c r="H118" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="39" t="n">
+      <c r="A119" s="40" t="n">
         <v>2030</v>
       </c>
-      <c r="B119" s="24" t="inlineStr">
+      <c r="B119" s="25" t="inlineStr">
         <is>
           <t>カネコ　コウタロウ</t>
         </is>
       </c>
-      <c r="C119" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D119" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E119" s="39" t="n">
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G119" s="24" t="inlineStr">
+      <c r="F119" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H119" s="24" t="inlineStr">
+      <c r="H119" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="39" t="n">
+      <c r="A120" s="40" t="n">
         <v>2040</v>
       </c>
-      <c r="B120" s="24" t="inlineStr">
+      <c r="B120" s="25" t="inlineStr">
         <is>
           <t>ハガ　レイコ</t>
         </is>
       </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D120" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E120" s="39" t="n">
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D120" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G120" s="24" t="inlineStr">
+      <c r="F120" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H120" s="24" t="inlineStr">
+      <c r="H120" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="39" t="n">
+      <c r="A121" s="40" t="n">
         <v>2041</v>
       </c>
-      <c r="B121" s="24" t="inlineStr">
+      <c r="B121" s="25" t="inlineStr">
         <is>
           <t>カイ　カヨ</t>
         </is>
       </c>
-      <c r="C121" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D121" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E121" s="39" t="n">
+      <c r="C121" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D121" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F121" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G121" s="24" t="inlineStr">
+      <c r="F121" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H121" s="24" t="inlineStr">
+      <c r="H121" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="39" t="n">
+      <c r="A122" s="40" t="n">
         <v>2042</v>
       </c>
-      <c r="B122" s="24" t="inlineStr">
+      <c r="B122" s="25" t="inlineStr">
         <is>
           <t>サトウ　トオル</t>
         </is>
       </c>
-      <c r="C122" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D122" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E122" s="39" t="n">
+      <c r="C122" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D122" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G122" s="24" t="inlineStr">
+      <c r="F122" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H122" s="24" t="inlineStr">
+      <c r="H122" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="39" t="n">
+      <c r="A123" s="40" t="n">
         <v>2044</v>
       </c>
-      <c r="B123" s="24" t="inlineStr">
+      <c r="B123" s="25" t="inlineStr">
         <is>
           <t>ヤマモト　ユウスケ</t>
         </is>
       </c>
-      <c r="C123" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D123" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E123" s="39" t="n">
+      <c r="C123" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D123" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G123" s="24" t="inlineStr">
+      <c r="F123" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G123" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H123" s="24" t="inlineStr">
+      <c r="H123" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="39" t="n">
+      <c r="A124" s="40" t="n">
         <v>2046</v>
       </c>
-      <c r="B124" s="24" t="inlineStr">
+      <c r="B124" s="25" t="inlineStr">
         <is>
           <t>イシカワ　シュウヘイ</t>
         </is>
       </c>
-      <c r="C124" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D124" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E124" s="39" t="n">
+      <c r="C124" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D124" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F124" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G124" s="24" t="inlineStr">
+      <c r="F124" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G124" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H124" s="24" t="inlineStr">
+      <c r="H124" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="39" t="n">
+      <c r="A125" s="40" t="n">
         <v>2066</v>
       </c>
-      <c r="B125" s="24" t="inlineStr">
+      <c r="B125" s="25" t="inlineStr">
         <is>
           <t>テラジマ　ヨシアキ</t>
         </is>
       </c>
-      <c r="C125" s="39" t="inlineStr">
-        <is>
-          <t>4回券</t>
-        </is>
-      </c>
-      <c r="D125" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E125" s="39" t="n">
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>4回券</t>
+        </is>
+      </c>
+      <c r="D125" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F125" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G125" s="24" t="inlineStr">
+      <c r="F125" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G125" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H125" s="24" t="inlineStr">
+      <c r="H125" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="39" t="n">
+      <c r="A126" s="40" t="n">
         <v>2022</v>
       </c>
-      <c r="B126" s="24" t="inlineStr">
+      <c r="B126" s="25" t="inlineStr">
         <is>
           <t>オオハシ　タツエ</t>
         </is>
       </c>
-      <c r="C126" s="39" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D126" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E126" s="39" t="n">
+      <c r="D126" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F126" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G126" s="24" t="inlineStr">
+      <c r="F126" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G126" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H126" s="24" t="inlineStr">
+      <c r="H126" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="39" t="n">
+      <c r="A127" s="40" t="n">
         <v>2025</v>
       </c>
-      <c r="B127" s="24" t="inlineStr">
+      <c r="B127" s="25" t="inlineStr">
         <is>
           <t>アライ　シンスケ</t>
         </is>
       </c>
-      <c r="C127" s="39" t="inlineStr">
+      <c r="C127" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D127" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E127" s="39" t="n">
+      <c r="D127" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G127" s="24" t="inlineStr">
+      <c r="F127" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G127" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H127" s="24" t="inlineStr">
+      <c r="H127" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="39" t="n">
+      <c r="A128" s="40" t="n">
         <v>2034</v>
       </c>
-      <c r="B128" s="24" t="inlineStr">
+      <c r="B128" s="25" t="inlineStr">
         <is>
           <t>タナベ　ナナエ</t>
         </is>
       </c>
-      <c r="C128" s="39" t="inlineStr">
+      <c r="C128" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D128" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E128" s="39" t="n">
+      <c r="D128" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F128" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G128" s="24" t="inlineStr">
+      <c r="F128" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H128" s="24" t="inlineStr">
+      <c r="H128" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="39" t="n">
+      <c r="A129" s="40" t="n">
         <v>2037</v>
       </c>
-      <c r="B129" s="24" t="inlineStr">
+      <c r="B129" s="25" t="inlineStr">
         <is>
           <t>タナベ　ヒロユキ</t>
         </is>
       </c>
-      <c r="C129" s="39" t="inlineStr">
+      <c r="C129" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D129" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E129" s="39" t="n">
+      <c r="D129" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F129" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G129" s="24" t="inlineStr">
+      <c r="F129" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G129" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H129" s="24" t="inlineStr">
+      <c r="H129" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="39" t="n">
+      <c r="A130" s="40" t="n">
         <v>2063</v>
       </c>
-      <c r="B130" s="24" t="inlineStr">
+      <c r="B130" s="25" t="inlineStr">
         <is>
           <t>ハツタ　ユウスケ</t>
         </is>
       </c>
-      <c r="C130" s="39" t="inlineStr">
+      <c r="C130" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D130" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E130" s="39" t="n">
+      <c r="D130" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G130" s="24" t="inlineStr">
+      <c r="F130" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G130" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H130" s="24" t="inlineStr">
+      <c r="H130" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="39" t="n">
+      <c r="A131" s="40" t="n">
         <v>2065</v>
       </c>
-      <c r="B131" s="24" t="inlineStr">
+      <c r="B131" s="25" t="inlineStr">
         <is>
           <t>スズキ　ヒサキ</t>
         </is>
       </c>
-      <c r="C131" s="39" t="inlineStr">
+      <c r="C131" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D131" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E131" s="39" t="n">
+      <c r="D131" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F131" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G131" s="24" t="inlineStr">
+      <c r="F131" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H131" s="24" t="inlineStr">
+      <c r="H131" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="39" t="n">
+      <c r="A132" s="40" t="n">
         <v>2068</v>
       </c>
-      <c r="B132" s="24" t="inlineStr">
+      <c r="B132" s="25" t="inlineStr">
         <is>
           <t>エンドウ　ユキエ</t>
         </is>
       </c>
-      <c r="C132" s="39" t="inlineStr">
+      <c r="C132" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D132" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E132" s="39" t="n">
+      <c r="D132" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E132" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F132" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G132" s="24" t="inlineStr">
+      <c r="F132" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G132" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H132" s="24" t="inlineStr">
+      <c r="H132" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="39" t="n">
+      <c r="A133" s="40" t="n">
         <v>2069</v>
       </c>
-      <c r="B133" s="24" t="inlineStr">
+      <c r="B133" s="25" t="inlineStr">
         <is>
           <t>タナカ　ヨネコ</t>
         </is>
       </c>
-      <c r="C133" s="39" t="inlineStr">
+      <c r="C133" s="40" t="inlineStr">
         <is>
           <t>8回券</t>
         </is>
       </c>
-      <c r="D133" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E133" s="39" t="n">
+      <c r="D133" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E133" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="F133" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G133" s="24" t="inlineStr">
+      <c r="F133" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" s="25" t="inlineStr">
         <is>
           <t>算出不可（都度）</t>
         </is>
       </c>
-      <c r="H133" s="24" t="inlineStr">
+      <c r="H133" s="25" t="inlineStr">
         <is>
           <t>都度</t>
         </is>
